--- a/results/abnmac/abnmac_classA_Ru40_Rv20_SCL32/classA_Ru40_Rv20_SCL_L32.xlsx
+++ b/results/abnmac/abnmac_classA_Ru40_Rv20_SCL32/classA_Ru40_Rv20_SCL_L32.xlsx
@@ -473,7 +473,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ABN-MAC — Class A, (Ru=0.40, Rv=0.20), SCL (L=32), analytic design</t>
+          <t>ABN-MAC — Class A, (Ru=0.40, Rv=0.20), SCL (L=32)</t>
         </is>
       </c>
     </row>
